--- a/temp/data-source-complete.xlsx
+++ b/temp/data-source-complete.xlsx
@@ -406,41 +406,41 @@
       <c r="B1" t="str">
         <v/>
       </c>
-      <c r="C1">
-        <v>2018</v>
-      </c>
-      <c r="D1">
-        <v>2019</v>
-      </c>
-      <c r="E1">
-        <v>2020</v>
-      </c>
-      <c r="F1">
-        <v>2020</v>
-      </c>
-      <c r="G1">
-        <v>2021</v>
-      </c>
-      <c r="H1">
-        <v>2022</v>
-      </c>
-      <c r="I1">
-        <v>2023</v>
-      </c>
-      <c r="J1">
-        <v>2023</v>
-      </c>
-      <c r="K1">
-        <v>2024</v>
-      </c>
-      <c r="L1">
-        <v>2024</v>
-      </c>
-      <c r="M1">
-        <v>2025</v>
-      </c>
-      <c r="N1">
-        <v>2025</v>
+      <c r="C1" t="str">
+        <v>2018年底</v>
+      </c>
+      <c r="D1" t="str">
+        <v>2019年底</v>
+      </c>
+      <c r="E1" t="str">
+        <v>2020年6月底</v>
+      </c>
+      <c r="F1" t="str">
+        <v>2020年底</v>
+      </c>
+      <c r="G1" t="str">
+        <v>2021年6月底</v>
+      </c>
+      <c r="H1" t="str">
+        <v>2022年5月底</v>
+      </c>
+      <c r="I1" t="str">
+        <v>2023年6月底</v>
+      </c>
+      <c r="J1" t="str">
+        <v>2023年9月底</v>
+      </c>
+      <c r="K1" t="str">
+        <v>2024年6月底</v>
+      </c>
+      <c r="L1" t="str">
+        <v>2024年9月底</v>
+      </c>
+      <c r="M1" t="str">
+        <v>2025年6月底</v>
+      </c>
+      <c r="N1" t="str">
+        <v>2025年9月底</v>
       </c>
     </row>
     <row r="2">
